--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484187_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484187_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1.6238</v>
+        <v>2.4221</v>
       </c>
       <c r="E2" t="n">
-        <v>3.4177</v>
+        <v>4.1319</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.7939</v>
+        <v>-1.7098</v>
       </c>
       <c r="G2" t="n">
         <v>0.0366</v>
@@ -610,13 +610,13 @@
         <v>0.7935</v>
       </c>
       <c r="S2" t="n">
-        <v>-2.0241</v>
+        <v>-1.2258</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.7877999999999999</v>
+        <v>-0.0736</v>
       </c>
       <c r="U2" t="n">
-        <v>-1.2363</v>
+        <v>-1.1522</v>
       </c>
       <c r="V2" t="n">
         <v>3.0162</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.1703</v>
+        <v>0.4124</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.2404</v>
+        <v>0.2301</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0701</v>
+        <v>0.1823</v>
       </c>
       <c r="G3" t="n">
         <v>-0.0151</v>
@@ -688,13 +688,13 @@
         <v>0.3968</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.5123</v>
+        <v>-0.9296</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.6744</v>
+        <v>-0.204</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.8378</v>
+        <v>-0.7256</v>
       </c>
       <c r="V3" t="n">
         <v>1.9522</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>G. PARDOS MARTINEZ</t>
+          <t>M. SMITH</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.3425</v>
+        <v>-0.201</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.4845</v>
+        <v>2.7372</v>
       </c>
       <c r="F4" t="n">
-        <v>0.142</v>
+        <v>-2.9383</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.5857</v>
+        <v>0.4031</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.6855</v>
+        <v>-0.3886</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0998</v>
+        <v>0.7916</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.4789</v>
+        <v>2.0214</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.5592</v>
+        <v>0.7311</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0803</v>
+        <v>1.2903</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.1068</v>
+        <v>-1.6183</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.1263</v>
+        <v>-1.1197</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0195</v>
+        <v>-0.4986</v>
       </c>
       <c r="P4" t="n">
-        <v>0.3968</v>
+        <v>-0.1984</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-1.1903</v>
       </c>
       <c r="R4" t="n">
-        <v>0.3968</v>
+        <v>0.9919</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.1536</v>
+        <v>-1.0089</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0056</v>
+        <v>0.0965</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.148</v>
+        <v>-1.1054</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>0.6032</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.8097</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-1.2065</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. SMITH</t>
+          <t>J. NEBRA SANCHEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.5797</v>
+        <v>-0.359</v>
       </c>
       <c r="E5" t="n">
-        <v>2.4708</v>
+        <v>0.8463000000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>-3.0505</v>
+        <v>-1.2054</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4031</v>
+        <v>0.2545</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.3886</v>
+        <v>0.2415</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7916</v>
+        <v>0.013</v>
       </c>
       <c r="J5" t="n">
-        <v>2.0214</v>
+        <v>0.1613</v>
       </c>
       <c r="K5" t="n">
-        <v>0.7311</v>
+        <v>0.1613</v>
       </c>
       <c r="L5" t="n">
-        <v>1.2903</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.6183</v>
+        <v>0.09320000000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.1197</v>
+        <v>0.08019999999999999</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.4986</v>
+        <v>0.013</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.1984</v>
+        <v>0.3968</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.1903</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9919</v>
+        <v>0.3968</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.3876</v>
+        <v>-1.0103</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1699</v>
+        <v>-0.5214</v>
       </c>
       <c r="U5" t="n">
-        <v>-1.2176</v>
+        <v>-0.4889</v>
       </c>
       <c r="V5" t="n">
-        <v>0.6032</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.8097</v>
+        <v>1.2065</v>
       </c>
       <c r="X5" t="n">
         <v>-1.2065</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. NEBRA SANCHEZ</t>
+          <t>S. RODRIGUEZ ALEJANDRE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.6575</v>
+        <v>-0.6806</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7443</v>
+        <v>-0.4689</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.4018</v>
+        <v>-0.2117</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2545</v>
+        <v>1.0227</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2415</v>
+        <v>0.8867</v>
       </c>
       <c r="I6" t="n">
-        <v>0.013</v>
+        <v>0.136</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1613</v>
+        <v>0.3279</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1613</v>
+        <v>1.0081</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>-0.6802</v>
       </c>
       <c r="M6" t="n">
-        <v>0.09320000000000001</v>
+        <v>0.6949</v>
       </c>
       <c r="N6" t="n">
-        <v>0.08019999999999999</v>
+        <v>-0.1214</v>
       </c>
       <c r="O6" t="n">
-        <v>0.013</v>
+        <v>0.8162</v>
       </c>
       <c r="P6" t="n">
-        <v>0.3968</v>
+        <v>-1.1903</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-1.1903</v>
       </c>
       <c r="R6" t="n">
-        <v>0.3968</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.3088</v>
+        <v>-0.8502</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.6235000000000001</v>
+        <v>-0.2097</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.6853</v>
+        <v>-0.6405</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.3373</v>
       </c>
       <c r="W6" t="n">
-        <v>1.2065</v>
+        <v>0.6032</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.2065</v>
+        <v>-0.266</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S. RODRIGUEZ ALEJANDRE</t>
+          <t>G. PARDOS MARTINEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.8449</v>
+        <v>-0.845</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.6333</v>
+        <v>-0.7906</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.2117</v>
+        <v>-0.0544</v>
       </c>
       <c r="G7" t="n">
-        <v>1.0227</v>
+        <v>-0.5857</v>
       </c>
       <c r="H7" t="n">
-        <v>0.8867</v>
+        <v>-0.6855</v>
       </c>
       <c r="I7" t="n">
-        <v>0.136</v>
+        <v>0.0998</v>
       </c>
       <c r="J7" t="n">
-        <v>0.3279</v>
+        <v>-0.4789</v>
       </c>
       <c r="K7" t="n">
-        <v>1.0081</v>
+        <v>-0.5592</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.6802</v>
+        <v>0.0803</v>
       </c>
       <c r="M7" t="n">
-        <v>0.6949</v>
+        <v>-0.1068</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.1214</v>
+        <v>-0.1263</v>
       </c>
       <c r="O7" t="n">
-        <v>0.8162</v>
+        <v>0.0195</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.1903</v>
+        <v>0.3968</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.1903</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>0.3968</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.0146</v>
+        <v>-0.6561</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3741</v>
+        <v>-0.3117</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.6405</v>
+        <v>-0.3444</v>
       </c>
       <c r="V7" t="n">
-        <v>0.3373</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0.6032</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.266</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.737</v>
+        <v>-1.4884</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.5033</v>
+        <v>-0.3389</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.2337</v>
+        <v>-1.1495</v>
       </c>
       <c r="G8" t="n">
         <v>0.008500000000000001</v>
@@ -1078,13 +1078,13 @@
         <v>0.5952</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.1342</v>
+        <v>-0.8857</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.6858</v>
+        <v>-0.5214</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4484</v>
+        <v>-0.3642</v>
       </c>
       <c r="V8" t="n">
         <v>-1.2065</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.273</v>
+        <v>-2.9693</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.949</v>
+        <v>-2.5611</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.324</v>
+        <v>-0.4082</v>
       </c>
       <c r="G9" t="n">
         <v>-2.2731</v>
@@ -1156,13 +1156,13 @@
         <v>0.9919</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0675</v>
+        <v>-0.7638</v>
       </c>
       <c r="T9" t="n">
-        <v>0.5613</v>
+        <v>-0.0509</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.6287</v>
+        <v>-0.7129</v>
       </c>
       <c r="V9" t="n">
         <v>0.266</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.7243</v>
+        <v>-5.1784</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.9032</v>
+        <v>-3.4134</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.8211</v>
+        <v>-1.765</v>
       </c>
       <c r="G10" t="n">
         <v>-2.0808</v>
@@ -1234,13 +1234,13 @@
         <v>1.3887</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.0646</v>
+        <v>-0.5185999999999999</v>
       </c>
       <c r="T10" t="n">
-        <v>0.5103</v>
+        <v>0.0001</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.5748</v>
+        <v>-0.5187</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.0672</v>
+        <v>-6.5736</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.4736</v>
+        <v>-1.6154</v>
       </c>
       <c r="F11" t="n">
-        <v>-4.5936</v>
+        <v>-4.9583</v>
       </c>
       <c r="G11" t="n">
         <v>-2.0904</v>
@@ -1312,13 +1312,13 @@
         <v>0.9919</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3736</v>
+        <v>-0.88</v>
       </c>
       <c r="T11" t="n">
-        <v>0.3232</v>
+        <v>0.1815</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.6968</v>
+        <v>-1.0615</v>
       </c>
       <c r="V11" t="n">
         <v>-2.4129</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-15.7726</v>
+        <v>-15.4608</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.554500000000001</v>
+        <v>-1.242800000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>-14.2182</v>
+        <v>-14.2183</v>
       </c>
       <c r="G12" t="n">
         <v>-5.319699999999999</v>
@@ -1363,7 +1363,7 @@
         <v>-4.664000000000001</v>
       </c>
       <c r="J12" t="n">
-        <v>2.3059</v>
+        <v>2.305899999999999</v>
       </c>
       <c r="K12" t="n">
         <v>4.541599999999999</v>
@@ -1390,13 +1390,13 @@
         <v>6.9435</v>
       </c>
       <c r="S12" t="n">
-        <v>-9.040899999999999</v>
+        <v>-8.729000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.9263</v>
+        <v>-1.6146</v>
       </c>
       <c r="U12" t="n">
-        <v>-7.1142</v>
+        <v>-7.1143</v>
       </c>
       <c r="V12" t="n">
         <v>2.5555</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>11.69</v>
+        <v>10.2455</v>
       </c>
       <c r="E13" t="n">
-        <v>10.963</v>
+        <v>9.330500000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7271</v>
+        <v>0.915</v>
       </c>
       <c r="G13" t="n">
         <v>4.921</v>
@@ -1468,13 +1468,13 @@
         <v>1.9838</v>
       </c>
       <c r="S13" t="n">
-        <v>3.4355</v>
+        <v>1.991</v>
       </c>
       <c r="T13" t="n">
-        <v>3.4067</v>
+        <v>1.7743</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0288</v>
+        <v>0.2167</v>
       </c>
       <c r="V13" t="n">
         <v>2.3417</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.2691</v>
+        <v>5.1349</v>
       </c>
       <c r="E14" t="n">
-        <v>5.3859</v>
+        <v>4.0595</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8833</v>
+        <v>1.0754</v>
       </c>
       <c r="G14" t="n">
         <v>3.7259</v>
@@ -1546,13 +1546,13 @@
         <v>0.3968</v>
       </c>
       <c r="S14" t="n">
-        <v>2.4124</v>
+        <v>1.2782</v>
       </c>
       <c r="T14" t="n">
-        <v>2.2957</v>
+        <v>0.9693000000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1167</v>
+        <v>0.3089</v>
       </c>
       <c r="V14" t="n">
         <v>-0.266</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.3141</v>
+        <v>2.32</v>
       </c>
       <c r="E15" t="n">
-        <v>2.3092</v>
+        <v>2.2072</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0049</v>
+        <v>0.1128</v>
       </c>
       <c r="G15" t="n">
         <v>-0.1887</v>
@@ -1624,13 +1624,13 @@
         <v>0.7935</v>
       </c>
       <c r="S15" t="n">
-        <v>0.5028</v>
+        <v>0.5087</v>
       </c>
       <c r="T15" t="n">
-        <v>0.4422</v>
+        <v>0.3401</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0606</v>
+        <v>0.1686</v>
       </c>
       <c r="V15" t="n">
         <v>1.2065</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. VIEYTES VERDU</t>
+          <t>X. ELVIRA GOMEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.4975</v>
+        <v>1.3801</v>
       </c>
       <c r="E16" t="n">
-        <v>0.1299</v>
+        <v>0.5048</v>
       </c>
       <c r="F16" t="n">
-        <v>1.3676</v>
+        <v>0.8752</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.2207</v>
+        <v>-1.1323</v>
       </c>
       <c r="H16" t="n">
-        <v>-2.6756</v>
+        <v>-0.1815</v>
       </c>
       <c r="I16" t="n">
-        <v>1.4549</v>
+        <v>-0.9509</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.5779</v>
+        <v>-0.3681</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.7477</v>
+        <v>0.0711</v>
       </c>
       <c r="L16" t="n">
-        <v>1.1698</v>
+        <v>-0.4392</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.6428</v>
+        <v>-0.7642</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.9278</v>
+        <v>-0.2525</v>
       </c>
       <c r="O16" t="n">
-        <v>0.2851</v>
+        <v>-0.5117</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.1984</v>
+        <v>1.5871</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.9919</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0.7935</v>
+        <v>1.5871</v>
       </c>
       <c r="S16" t="n">
-        <v>2.3846</v>
+        <v>0.9253</v>
       </c>
       <c r="T16" t="n">
-        <v>1.1678</v>
+        <v>0.873</v>
       </c>
       <c r="U16" t="n">
-        <v>1.2169</v>
+        <v>0.0524</v>
       </c>
       <c r="V16" t="n">
-        <v>0.532</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>0.532</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X. ELVIRA GOMEZ</t>
+          <t>M. VIEYTES VERDU</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9915</v>
+        <v>0.5767</v>
       </c>
       <c r="E17" t="n">
-        <v>0.5048</v>
+        <v>-0.4823</v>
       </c>
       <c r="F17" t="n">
-        <v>0.4867</v>
+        <v>1.059</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.1323</v>
+        <v>-1.2207</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.1815</v>
+        <v>-2.6756</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.9509</v>
+        <v>1.4549</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.3681</v>
+        <v>-0.5779</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0711</v>
+        <v>-1.7477</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.4392</v>
+        <v>1.1698</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.7642</v>
+        <v>-0.6428</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.2525</v>
+        <v>-0.9278</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.5117</v>
+        <v>0.2851</v>
       </c>
       <c r="P17" t="n">
-        <v>1.5871</v>
+        <v>-0.1984</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-0.9919</v>
       </c>
       <c r="R17" t="n">
-        <v>1.5871</v>
+        <v>0.7935</v>
       </c>
       <c r="S17" t="n">
-        <v>0.5368000000000001</v>
+        <v>1.4638</v>
       </c>
       <c r="T17" t="n">
-        <v>0.873</v>
+        <v>0.5556</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3362</v>
+        <v>0.9082</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.532</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.532</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. DOMENGE CABRER</t>
+          <t>V. VINÓS ALTEMIR</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1816</v>
+        <v>0.1873</v>
       </c>
       <c r="E18" t="n">
-        <v>1.2802</v>
+        <v>1.4906</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.0986</v>
+        <v>-1.3033</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.6097</v>
+        <v>2.3409</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.7458</v>
+        <v>0.3224</v>
       </c>
       <c r="I18" t="n">
-        <v>0.136</v>
+        <v>2.0185</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.6802</v>
+        <v>2.6411</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.6802</v>
+        <v>1.3158</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.3253</v>
       </c>
       <c r="M18" t="n">
-        <v>0.07049999999999999</v>
+        <v>-0.3002</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.06560000000000001</v>
+        <v>-0.9933999999999999</v>
       </c>
       <c r="O18" t="n">
-        <v>0.136</v>
+        <v>0.6932</v>
       </c>
       <c r="P18" t="n">
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-0.9919</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>0.9919</v>
       </c>
       <c r="S18" t="n">
-        <v>0.7913</v>
+        <v>0.2593</v>
       </c>
       <c r="T18" t="n">
-        <v>0.7539</v>
+        <v>-0.1586</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0374</v>
+        <v>0.418</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-2.4129</v>
       </c>
       <c r="W18" t="n">
-        <v>1.2065</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.2065</v>
+        <v>-2.4129</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.7386</v>
+        <v>0.1397</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.9073</v>
+        <v>-1.1931</v>
       </c>
       <c r="F19" t="n">
-        <v>1.1686</v>
+        <v>1.3327</v>
       </c>
       <c r="G19" t="n">
         <v>-0.5014</v>
@@ -1936,13 +1936,13 @@
         <v>1.3887</v>
       </c>
       <c r="S19" t="n">
-        <v>0.1434</v>
+        <v>1.0217</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1303</v>
+        <v>0.5839</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2737</v>
+        <v>0.4378</v>
       </c>
       <c r="V19" t="n">
         <v>1.2065</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>V. VINÓS ALTEMIR</t>
+          <t>E. IBAEZ ALDAZABAL</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.7471</v>
+        <v>-0.07389999999999999</v>
       </c>
       <c r="E20" t="n">
-        <v>0.7764</v>
+        <v>-1.3347</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.5235</v>
+        <v>1.2609</v>
       </c>
       <c r="G20" t="n">
-        <v>2.3409</v>
+        <v>-0.8593</v>
       </c>
       <c r="H20" t="n">
-        <v>0.3224</v>
+        <v>-1.9151</v>
       </c>
       <c r="I20" t="n">
-        <v>2.0185</v>
+        <v>1.0558</v>
       </c>
       <c r="J20" t="n">
-        <v>2.6411</v>
+        <v>-1.3065</v>
       </c>
       <c r="K20" t="n">
-        <v>1.3158</v>
+        <v>-1.7986</v>
       </c>
       <c r="L20" t="n">
-        <v>1.3253</v>
+        <v>0.4921</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.3002</v>
+        <v>0.4472</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.9933999999999999</v>
+        <v>-0.1165</v>
       </c>
       <c r="O20" t="n">
-        <v>0.6932</v>
+        <v>0.5637</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>0.9919</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9919</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
         <v>0.9919</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.6751</v>
+        <v>0.734</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.8728</v>
+        <v>0.6463</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1978</v>
+        <v>0.0878</v>
       </c>
       <c r="V20" t="n">
-        <v>-2.4129</v>
+        <v>-0.9405</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>-0.6745</v>
       </c>
       <c r="X20" t="n">
-        <v>-2.4129</v>
+        <v>-0.266</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>D. NGUBA ETAME</t>
+          <t>J. DOMENGE CABRER</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,64 +2047,64 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.8645</v>
+        <v>-0.1704</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.6825</v>
+        <v>0.872</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.1819</v>
+        <v>-1.0425</v>
       </c>
       <c r="G21" t="n">
-        <v>0.4179</v>
+        <v>-0.6097</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.3024</v>
+        <v>-0.7458</v>
       </c>
       <c r="I21" t="n">
-        <v>0.7204</v>
+        <v>0.136</v>
       </c>
       <c r="J21" t="n">
-        <v>0.06560000000000001</v>
+        <v>-0.6802</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0255</v>
+        <v>-0.6802</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0402</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0.3523</v>
+        <v>0.07049999999999999</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.3279</v>
+        <v>-0.06560000000000001</v>
       </c>
       <c r="O21" t="n">
-        <v>0.6802</v>
+        <v>0.136</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.5952</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.9919</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.3968</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>0.5192</v>
+        <v>0.4393</v>
       </c>
       <c r="T21" t="n">
-        <v>0.2438</v>
+        <v>0.3458</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2754</v>
+        <v>0.0935</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.2065</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.2065</v>
       </c>
       <c r="X21" t="n">
         <v>-1.2065</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>E. IBAEZ ALDAZABAL</t>
+          <t>D. NGUBA ETAME</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.004</v>
+        <v>-0.6042999999999999</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.049</v>
+        <v>-0.4785</v>
       </c>
       <c r="F22" t="n">
-        <v>1.0449</v>
+        <v>-0.1258</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.8593</v>
+        <v>0.4179</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.9151</v>
+        <v>-0.3024</v>
       </c>
       <c r="I22" t="n">
-        <v>1.0558</v>
+        <v>0.7204</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.3065</v>
+        <v>0.06560000000000001</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.7986</v>
+        <v>0.0255</v>
       </c>
       <c r="L22" t="n">
-        <v>0.4921</v>
+        <v>0.0402</v>
       </c>
       <c r="M22" t="n">
-        <v>0.4472</v>
+        <v>0.3523</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.1165</v>
+        <v>-0.3279</v>
       </c>
       <c r="O22" t="n">
-        <v>0.5637</v>
+        <v>0.6802</v>
       </c>
       <c r="P22" t="n">
-        <v>0.9919</v>
+        <v>-0.5952</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-0.9919</v>
       </c>
       <c r="R22" t="n">
-        <v>0.9919</v>
+        <v>0.3968</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.1961</v>
+        <v>0.7794</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.0679</v>
+        <v>0.4478</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1282</v>
+        <v>0.3315</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.9405</v>
+        <v>-1.2065</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.6745</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.266</v>
+        <v>-1.2065</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>T. WRIGHT</t>
+          <t>M. DUCH CABEZAS</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,40 +2203,40 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.8762</v>
+        <v>-0.7845</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.2575</v>
+        <v>-1.2146</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.6187</v>
+        <v>0.4301</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.07199999999999999</v>
+        <v>-1.5019</v>
       </c>
       <c r="H23" t="n">
-        <v>0.292</v>
+        <v>-0.2776</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.364</v>
+        <v>-1.2244</v>
       </c>
       <c r="J23" t="n">
-        <v>0.2413</v>
+        <v>-1.7361</v>
       </c>
       <c r="K23" t="n">
-        <v>0.0806</v>
+        <v>0.1815</v>
       </c>
       <c r="L23" t="n">
-        <v>0.1606</v>
+        <v>-1.9175</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.3133</v>
+        <v>0.2342</v>
       </c>
       <c r="N23" t="n">
-        <v>0.2114</v>
+        <v>-0.459</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.5247000000000001</v>
+        <v>0.6932</v>
       </c>
       <c r="P23" t="n">
         <v>0.7935</v>
@@ -2248,28 +2248,28 @@
         <v>0.7935</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.1848</v>
+        <v>0.5271</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.4988</v>
+        <v>0.5215</v>
       </c>
       <c r="U23" t="n">
-        <v>0.314</v>
+        <v>0.0056</v>
       </c>
       <c r="V23" t="n">
-        <v>-2.4129</v>
+        <v>-0.6032</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-2.4129</v>
+        <v>-0.6032</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>M. DUCH CABEZAS</t>
+          <t>T. WRIGHT</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,40 +2281,40 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.9408</v>
+        <v>-1.2181</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.2349</v>
+        <v>0.4567</v>
       </c>
       <c r="F24" t="n">
-        <v>0.294</v>
+        <v>-1.6748</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.5019</v>
+        <v>-0.07199999999999999</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.2776</v>
+        <v>0.292</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.2244</v>
+        <v>-0.364</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.7361</v>
+        <v>0.2413</v>
       </c>
       <c r="K24" t="n">
-        <v>0.1815</v>
+        <v>0.0806</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.9175</v>
+        <v>0.1606</v>
       </c>
       <c r="M24" t="n">
-        <v>0.2342</v>
+        <v>-0.3133</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.459</v>
+        <v>0.2114</v>
       </c>
       <c r="O24" t="n">
-        <v>0.6932</v>
+        <v>-0.5247000000000001</v>
       </c>
       <c r="P24" t="n">
         <v>0.7935</v>
@@ -2326,22 +2326,22 @@
         <v>0.7935</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.6292</v>
+        <v>0.4733</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.4988</v>
+        <v>0.2154</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.1304</v>
+        <v>0.2579</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.6032</v>
+        <v>-2.4129</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.6032</v>
+        <v>-2.4129</v>
       </c>
     </row>
     <row r="25">
@@ -2359,31 +2359,31 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>15.7726</v>
+        <v>17.133</v>
       </c>
       <c r="E25" t="n">
-        <v>14.2182</v>
+        <v>14.2181</v>
       </c>
       <c r="F25" t="n">
-        <v>1.5544</v>
+        <v>2.9147</v>
       </c>
       <c r="G25" t="n">
         <v>5.319700000000001</v>
       </c>
       <c r="H25" t="n">
-        <v>0.6558000000000002</v>
+        <v>0.6558000000000004</v>
       </c>
       <c r="I25" t="n">
-        <v>4.663799999999998</v>
+        <v>4.6638</v>
       </c>
       <c r="J25" t="n">
-        <v>7.6256</v>
+        <v>7.625599999999999</v>
       </c>
       <c r="K25" t="n">
         <v>5.1974</v>
       </c>
       <c r="L25" t="n">
-        <v>2.4283</v>
+        <v>2.428299999999999</v>
       </c>
       <c r="M25" t="n">
         <v>-2.3058</v>
@@ -2395,7 +2395,7 @@
         <v>2.2356</v>
       </c>
       <c r="P25" t="n">
-        <v>3.9675</v>
+        <v>3.967499999999999</v>
       </c>
       <c r="Q25" t="n">
         <v>-6.9434</v>
@@ -2404,19 +2404,19 @@
         <v>10.911</v>
       </c>
       <c r="S25" t="n">
-        <v>9.040800000000001</v>
+        <v>10.4011</v>
       </c>
       <c r="T25" t="n">
-        <v>7.1145</v>
+        <v>7.114399999999999</v>
       </c>
       <c r="U25" t="n">
-        <v>1.9265</v>
+        <v>3.2869</v>
       </c>
       <c r="V25" t="n">
-        <v>-2.555300000000001</v>
+        <v>-2.5553</v>
       </c>
       <c r="W25" t="n">
-        <v>6.421899999999999</v>
+        <v>6.4219</v>
       </c>
       <c r="X25" t="n">
         <v>-8.9772</v>
